--- a/src/assets/docs/modeloGDR.xlsx
+++ b/src/assets/docs/modeloGDR.xlsx
@@ -302,497 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia de 1er avance de meta (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I21" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fecha de entrega de 1er avance (obligatorio)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J21" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Respecto a la evidencia de avance.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N21" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Para obtener el puntaje de la meta, debe estar definido:
-1. El "Segmento" del evaluado.
-2. El "Sentido del indicador" de la meta.
-3. El "valor esperado" de la meta.
-4. El "peso" de la meta
-El "valor alcanzado" debe tener la misma unidad de medida que el "valor esperado" es decir, si el valor esperado es porcentaje, el valor alcanzado debe estar expresado también en porcentaje.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H22" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia final, para evaluación. (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I22" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fecha de entrega de evidencia final (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J22" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Respecto a la evidencia final
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H23" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia de 1er avance de meta (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I23" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fecha de entrega de 1er avance (obligatorio)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J23" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Respecto a la evidencia de avance.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N23" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Para obtener el puntaje de la meta, debe estar definido:
-1. El "Segmento" del evaluado.
-2. El "Sentido del indicador" de la meta.
-3. El "valor esperado" de la meta.
-4. El "peso" de la meta
-El "valor alcanzado" debe tener la misma unidad de medida que el "valor esperado" es decir, si el valor esperado es porcentaje, el valor alcanzado debe estar expresado también en porcentaje.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H24" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia final, para evaluación. (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I24" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fecha de entrega de evidencia final (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J24" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Respecto a la evidencia final
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H25" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia de 1er avance de meta (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I25" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fecha de entrega de 1er avance (obligatorio)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J25" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Respecto a la evidencia de avance.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N25" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Para obtener el puntaje de la meta, debe estar definido:
-1. El "Segmento" del evaluado.
-2. El "Sentido del indicador" de la meta.
-3. El "valor esperado" de la meta.
-4. El "peso" de la meta
-El "valor alcanzado" debe tener la misma unidad de medida que el "valor esperado" es decir, si el valor esperado es porcentaje, el valor alcanzado debe estar expresado también en porcentaje.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H26" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia final, para evaluación. (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I26" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fecha de entrega de evidencia final (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Respecto a la evidencia final
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H27" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia de 1er avance de meta (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I27" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fecha de entrega de 1er avance (obligatorio)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J27" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Respecto a la evidencia de avance.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N27" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Para obtener el puntaje de la meta, debe estar definido:
-1. El "Segmento" del evaluado.
-2. El "Sentido del indicador" de la meta.
-3. El "valor esperado" de la meta.
-4. El "peso" de la meta
-El "valor alcanzado" debe tener la misma unidad de medida que el "valor esperado" es decir, si el valor esperado es porcentaje, el valor alcanzado debe estar expresado también en porcentaje.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H28" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia final, para evaluación. (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I28" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fecha de entrega de evidencia final (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J28" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Respecto a la evidencia final
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H29" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia de 1er avance de meta (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I29" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fecha de entrega de 1er avance (obligatorio)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J29" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Respecto a la evidencia de avance.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N29" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Para obtener el puntaje de la meta, debe estar definido:
-1. El "Segmento" del evaluado.
-2. El "Sentido del indicador" de la meta.
-3. El "valor esperado" de la meta.
-4. El "peso" de la meta
-El "valor alcanzado" debe tener la misma unidad de medida que el "valor esperado" es decir, si el valor esperado es porcentaje, el valor alcanzado debe estar expresado también en porcentaje.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H30" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Evidencia final, para evaluación. (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I30" authorId="3" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fecha de entrega de evidencia final (obligatorio)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J30" authorId="1" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Respecto a la evidencia final
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B33" authorId="1" shapeId="0">
+    <comment ref="B38" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -805,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0">
+    <comment ref="I40" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -830,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B38" authorId="4" shapeId="0">
+    <comment ref="B43" authorId="4" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -859,7 +369,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="110">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -1010,9 +520,6 @@
   </si>
   <si>
     <t>COMENTARIOS</t>
-  </si>
-  <si>
-    <t>[Seleccione]</t>
   </si>
   <si>
     <t>PUNTUACIÓN FINAL</t>
@@ -1449,12 +956,6 @@
     <t>Firmas de la reunión de retroalimentación final</t>
   </si>
   <si>
-    <t>[dd/mmm/aaaa]</t>
-  </si>
-  <si>
-    <t>Tiene 6 meses o más desempeñando el puesto que es objeto de evaluación</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Se deberá completar con SI o NO, según corresponda. 
 Recuerde que de no asistir a la reunión de fijación de metas comunicada y agendada por razones atribuibles a su exclusiva responsabilidad, tendrá la calificación de </t>
@@ -1607,12 +1108,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="d&quot; de &quot;mmmm"/>
-    <numFmt numFmtId="167" formatCode="[$-1540A]dd\-mmm\-yyyy;@"/>
-  </numFmts>
   <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2571,7 +2066,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -2643,22 +2138,6 @@
     <xf numFmtId="0" fontId="17" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2710,17 +2189,86 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="15" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2766,41 +2314,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2818,6 +2331,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2841,46 +2357,99 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="31" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="31" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="14" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="31" fillId="14" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="31" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="32" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="32" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2896,84 +2465,51 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="15" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3012,65 +2548,14 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3103,14 +2588,6 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -3183,15 +2660,6 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3924,13 +3392,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>69454</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>142781</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>94854</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>522804</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4000,13 +3468,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>558417</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>238349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1060067</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>619349</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4076,7 +3544,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>929268</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="184731" cy="254557"/>
@@ -4498,46 +3966,46 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" s="52" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
+    <row r="2" spans="1:7" s="48" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
     </row>
     <row r="3" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="63" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
+      <c r="C3" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="46"/>
+      <c r="C5" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="42"/>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4552,12 +4020,12 @@
     <row r="7" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="69"/>
+      <c r="D7" s="86"/>
       <c r="E7" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="3"/>
@@ -4566,11 +4034,11 @@
       <c r="A8" s="1"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="44" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="1"/>
@@ -4579,11 +4047,11 @@
       <c r="A9" s="1"/>
       <c r="B9" s="7"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="48" t="s">
-        <v>65</v>
+      <c r="D9" s="44" t="s">
+        <v>64</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="1"/>
@@ -4592,11 +4060,11 @@
       <c r="A10" s="1"/>
       <c r="B10" s="7"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="44" t="s">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="1"/>
@@ -4605,11 +4073,11 @@
       <c r="A11" s="1"/>
       <c r="B11" s="7"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="44" t="s">
         <v>2</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="1"/>
@@ -4618,11 +4086,11 @@
       <c r="A12" s="1"/>
       <c r="B12" s="7"/>
       <c r="C12" s="10"/>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="44" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="1"/>
@@ -4631,11 +4099,11 @@
       <c r="A13" s="1"/>
       <c r="B13" s="7"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="44" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="1"/>
@@ -4660,24 +4128,24 @@
     </row>
     <row r="16" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14"/>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="76" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
+      <c r="B17" s="93" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -4688,7 +4156,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="1"/>
@@ -4697,11 +4165,11 @@
       <c r="A19" s="1"/>
       <c r="B19" s="16"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="66" t="s">
-        <v>80</v>
+      <c r="D19" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="83" t="s">
+        <v>79</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="1"/>
@@ -4710,8 +4178,8 @@
       <c r="A20" s="1"/>
       <c r="B20" s="16"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="67"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="84"/>
       <c r="F20" s="16"/>
       <c r="G20" s="1"/>
     </row>
@@ -4719,8 +4187,8 @@
       <c r="A21" s="1"/>
       <c r="B21" s="16"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="67"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="84"/>
       <c r="F21" s="16"/>
       <c r="G21" s="1"/>
     </row>
@@ -4728,8 +4196,8 @@
       <c r="A22" s="1"/>
       <c r="B22" s="16"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="67"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="84"/>
       <c r="F22" s="16"/>
       <c r="G22" s="1"/>
     </row>
@@ -4737,8 +4205,8 @@
       <c r="A23" s="1"/>
       <c r="B23" s="16"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="67"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="84"/>
       <c r="F23" s="16"/>
       <c r="G23" s="1"/>
     </row>
@@ -4746,8 +4214,8 @@
       <c r="A24" s="1"/>
       <c r="B24" s="16"/>
       <c r="C24" s="10"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="67"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="84"/>
       <c r="F24" s="16"/>
       <c r="G24" s="1"/>
     </row>
@@ -4755,8 +4223,8 @@
       <c r="A25" s="1"/>
       <c r="B25" s="16"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="68"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="85"/>
       <c r="F25" s="16"/>
       <c r="G25" s="1"/>
     </row>
@@ -4777,7 +4245,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="1"/>
@@ -4786,11 +4254,11 @@
       <c r="A28" s="1"/>
       <c r="B28" s="16"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="44" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="1"/>
@@ -4799,11 +4267,11 @@
       <c r="A29" s="1"/>
       <c r="B29" s="16"/>
       <c r="C29" s="10"/>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="51" t="s">
-        <v>82</v>
+      <c r="E29" s="47" t="s">
+        <v>81</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="1"/>
@@ -4812,11 +4280,11 @@
       <c r="A30" s="1"/>
       <c r="B30" s="16"/>
       <c r="C30" s="10"/>
-      <c r="D30" s="48" t="s">
-        <v>59</v>
+      <c r="D30" s="44" t="s">
+        <v>58</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="1"/>
@@ -4825,11 +4293,11 @@
       <c r="A31" s="1"/>
       <c r="B31" s="16"/>
       <c r="C31" s="10"/>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="44" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="1"/>
@@ -4838,11 +4306,11 @@
       <c r="A32" s="1"/>
       <c r="B32" s="16"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="48" t="s">
+      <c r="D32" s="44" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="1"/>
@@ -4851,11 +4319,11 @@
       <c r="A33" s="1"/>
       <c r="B33" s="16"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="44" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F33" s="16"/>
       <c r="G33" s="1"/>
@@ -4864,11 +4332,11 @@
       <c r="A34" s="1"/>
       <c r="B34" s="16"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="48" t="s">
-        <v>73</v>
+      <c r="D34" s="44" t="s">
+        <v>72</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="1"/>
@@ -4884,85 +4352,85 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
+      <c r="B36" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="92"/>
+      <c r="D36" s="92"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="92"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="45"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="8"/>
       <c r="D37" s="18" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F37" s="45"/>
+        <v>73</v>
+      </c>
+      <c r="F37" s="41"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" ht="78" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="45"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="10"/>
-      <c r="D38" s="48" t="s">
-        <v>67</v>
+      <c r="D38" s="44" t="s">
+        <v>66</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F38" s="45"/>
+        <v>82</v>
+      </c>
+      <c r="F38" s="41"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" ht="78" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="45"/>
+      <c r="B39" s="41"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="48" t="s">
-        <v>68</v>
+      <c r="D39" s="44" t="s">
+        <v>67</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="45"/>
+        <v>83</v>
+      </c>
+      <c r="F39" s="41"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" ht="78" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="45"/>
+      <c r="B40" s="41"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="48" t="s">
-        <v>69</v>
+      <c r="D40" s="44" t="s">
+        <v>68</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="45"/>
+        <v>84</v>
+      </c>
+      <c r="F40" s="41"/>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
+      <c r="B42" s="91" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="91"/>
+      <c r="D42" s="91"/>
+      <c r="E42" s="91"/>
+      <c r="F42" s="91"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -4973,7 +4441,7 @@
         <v>14</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F43" s="21"/>
       <c r="G43" s="1"/>
@@ -4982,11 +4450,11 @@
       <c r="A44" s="1"/>
       <c r="B44" s="21"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="49" t="s">
-        <v>63</v>
+      <c r="D44" s="45" t="s">
+        <v>62</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F44" s="21"/>
       <c r="G44" s="1"/>
@@ -4995,11 +4463,11 @@
       <c r="A45" s="1"/>
       <c r="B45" s="21"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="49" t="s">
+      <c r="D45" s="45" t="s">
         <v>15</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F45" s="21"/>
       <c r="G45" s="1"/>
@@ -5025,12 +4493,12 @@
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="22"/>
-      <c r="C48" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="65"/>
+      <c r="C48" s="82" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="82"/>
       <c r="E48" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F48" s="22"/>
       <c r="G48" s="1"/>
@@ -5039,11 +4507,11 @@
       <c r="A49" s="1"/>
       <c r="B49" s="22"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="E49" s="51" t="s">
-        <v>108</v>
+      <c r="D49" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>105</v>
       </c>
       <c r="F49" s="22"/>
       <c r="G49" s="1"/>
@@ -5052,11 +4520,11 @@
       <c r="A50" s="1"/>
       <c r="B50" s="22"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="49" t="s">
-        <v>107</v>
+      <c r="D50" s="45" t="s">
+        <v>104</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F50" s="22"/>
       <c r="G50" s="1"/>
@@ -5082,12 +4550,12 @@
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="4"/>
-      <c r="C53" s="64" t="s">
+      <c r="C53" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="64"/>
+      <c r="D53" s="81"/>
       <c r="E53" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="1"/>
@@ -5096,11 +4564,11 @@
       <c r="A54" s="1"/>
       <c r="B54" s="4"/>
       <c r="C54" s="8"/>
-      <c r="D54" s="50" t="s">
+      <c r="D54" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="E54" s="51" t="s">
-        <v>89</v>
+      <c r="E54" s="47" t="s">
+        <v>88</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="1"/>
@@ -5109,11 +4577,11 @@
       <c r="A55" s="1"/>
       <c r="B55" s="4"/>
       <c r="C55" s="10"/>
-      <c r="D55" s="50" t="s">
+      <c r="D55" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="51" t="s">
-        <v>90</v>
+      <c r="E55" s="47" t="s">
+        <v>89</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="1"/>
@@ -5122,11 +4590,11 @@
       <c r="A56" s="1"/>
       <c r="B56" s="4"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="50" t="s">
+      <c r="D56" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="54" t="s">
-        <v>91</v>
+      <c r="E56" s="50" t="s">
+        <v>90</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="1"/>
@@ -5135,11 +4603,11 @@
       <c r="A57" s="1"/>
       <c r="B57" s="4"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="50" t="s">
+      <c r="D57" s="46" t="s">
         <v>20</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="1"/>
@@ -5148,11 +4616,11 @@
       <c r="A58" s="1"/>
       <c r="B58" s="4"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="50" t="s">
-        <v>94</v>
+      <c r="D58" s="46" t="s">
+        <v>93</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="1"/>
@@ -5811,7 +5279,7 @@
   <sheetPr codeName="Hoja2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:N41"/>
+  <dimension ref="B1:N46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -5846,23 +5314,23 @@
       <c r="N1" s="24"/>
     </row>
     <row r="2" spans="2:14" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="142" t="s">
-        <v>110</v>
-      </c>
-      <c r="N2" s="143"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="153"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="155" t="s">
+        <v>107</v>
+      </c>
+      <c r="N2" s="156"/>
     </row>
     <row r="3" spans="2:14" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="26"/>
@@ -5880,23 +5348,23 @@
       <c r="N3" s="27"/>
     </row>
     <row r="4" spans="2:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="144" t="s">
+      <c r="B4" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="145"/>
-      <c r="D4" s="146" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="147"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="159" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
+      <c r="M4" s="159"/>
+      <c r="N4" s="160"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="28"/>
@@ -5914,171 +5382,171 @@
       <c r="N5" s="29"/>
     </row>
     <row r="6" spans="2:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="148" t="s">
+      <c r="B6" s="161" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="149"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="149"/>
-      <c r="N6" s="150"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="163"/>
     </row>
     <row r="7" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="151" t="s">
+      <c r="B7" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="151" t="s">
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="153"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="144"/>
+      <c r="L7" s="144"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="145"/>
     </row>
     <row r="8" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="161" t="s">
+      <c r="B8" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="162"/>
-      <c r="D8" s="163"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="166" t="s">
+      <c r="C8" s="133"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="167"/>
-      <c r="J8" s="168"/>
-      <c r="K8" s="159"/>
-      <c r="L8" s="159"/>
-      <c r="M8" s="159"/>
-      <c r="N8" s="160"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="129"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="130"/>
+      <c r="N8" s="131"/>
     </row>
     <row r="9" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="161" t="s">
+      <c r="B9" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="162"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="157"/>
-      <c r="F9" s="157"/>
-      <c r="G9" s="158"/>
-      <c r="H9" s="166" t="s">
+      <c r="C9" s="133"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="149"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="167"/>
-      <c r="J9" s="168"/>
-      <c r="K9" s="159"/>
-      <c r="L9" s="159"/>
-      <c r="M9" s="159"/>
-      <c r="N9" s="160"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="129"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="131"/>
     </row>
     <row r="10" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="154" t="s">
+      <c r="B10" s="146" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="155"/>
-      <c r="D10" s="156"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="154" t="s">
+      <c r="C10" s="147"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="149"/>
+      <c r="G10" s="150"/>
+      <c r="H10" s="146" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="155"/>
-      <c r="J10" s="155"/>
-      <c r="K10" s="159"/>
-      <c r="L10" s="159"/>
-      <c r="M10" s="159"/>
-      <c r="N10" s="160"/>
+      <c r="I10" s="147"/>
+      <c r="J10" s="147"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="130"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="131"/>
     </row>
     <row r="11" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="161" t="s">
+      <c r="B11" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="162"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="158"/>
-      <c r="H11" s="154" t="s">
+      <c r="C11" s="133"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="159"/>
-      <c r="L11" s="159"/>
-      <c r="M11" s="159"/>
-      <c r="N11" s="160"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
+      <c r="N11" s="131"/>
     </row>
     <row r="12" spans="2:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="154" t="s">
+      <c r="B12" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="155"/>
-      <c r="D12" s="156"/>
-      <c r="E12" s="157"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="158"/>
-      <c r="H12" s="154" t="s">
+      <c r="C12" s="147"/>
+      <c r="D12" s="148"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="150"/>
+      <c r="H12" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="155"/>
-      <c r="J12" s="155"/>
-      <c r="K12" s="159"/>
-      <c r="L12" s="159"/>
-      <c r="M12" s="159"/>
-      <c r="N12" s="160"/>
-    </row>
-    <row r="13" spans="2:14" s="56" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="55"/>
-      <c r="C13" s="205" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="205"/>
-      <c r="E13" s="205"/>
-      <c r="F13" s="205"/>
-      <c r="G13" s="205"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="205"/>
-      <c r="J13" s="205"/>
-      <c r="K13" s="205"/>
-      <c r="L13" s="205"/>
-      <c r="M13" s="205"/>
-      <c r="N13" s="205"/>
+      <c r="I12" s="147"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
+      <c r="M12" s="130"/>
+      <c r="N12" s="131"/>
+    </row>
+    <row r="13" spans="2:14" s="52" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="51"/>
+      <c r="C13" s="201" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="201"/>
+      <c r="H13" s="201"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="201"/>
+      <c r="K13" s="201"/>
+      <c r="L13" s="201"/>
+      <c r="M13" s="201"/>
+      <c r="N13" s="201"/>
     </row>
     <row r="14" spans="2:14" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="198" t="s">
+      <c r="B14" s="194" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="199"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="201"/>
-      <c r="F14" s="201"/>
-      <c r="G14" s="202"/>
-      <c r="H14" s="198" t="s">
+      <c r="C14" s="195"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="197"/>
+      <c r="F14" s="197"/>
+      <c r="G14" s="198"/>
+      <c r="H14" s="194" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="199"/>
-      <c r="J14" s="199"/>
-      <c r="K14" s="203"/>
-      <c r="L14" s="203"/>
-      <c r="M14" s="203"/>
-      <c r="N14" s="204"/>
+      <c r="I14" s="195"/>
+      <c r="J14" s="195"/>
+      <c r="K14" s="199"/>
+      <c r="L14" s="199"/>
+      <c r="M14" s="199"/>
+      <c r="N14" s="200"/>
     </row>
     <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="31"/>
@@ -6096,92 +5564,92 @@
       <c r="N15" s="31"/>
     </row>
     <row r="16" spans="2:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="206" t="s">
+      <c r="B16" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="207"/>
-      <c r="G16" s="207"/>
-      <c r="H16" s="207"/>
-      <c r="I16" s="207"/>
-      <c r="J16" s="207"/>
-      <c r="K16" s="207"/>
-      <c r="L16" s="207"/>
-      <c r="M16" s="207"/>
-      <c r="N16" s="208"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="165"/>
+      <c r="F16" s="165"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="165"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="165"/>
+      <c r="K16" s="165"/>
+      <c r="L16" s="165"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="166"/>
     </row>
     <row r="17" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="169" t="s">
+      <c r="B17" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="170"/>
-      <c r="D17" s="170"/>
-      <c r="E17" s="170"/>
-      <c r="F17" s="170"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="170"/>
-      <c r="I17" s="171"/>
-      <c r="J17" s="172" t="s">
+      <c r="C17" s="168"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="168"/>
+      <c r="H17" s="168"/>
+      <c r="I17" s="169"/>
+      <c r="J17" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="173"/>
-      <c r="L17" s="174"/>
-      <c r="M17" s="175" t="s">
+      <c r="K17" s="171"/>
+      <c r="L17" s="172"/>
+      <c r="M17" s="173" t="s">
         <v>33</v>
       </c>
-      <c r="N17" s="176"/>
+      <c r="N17" s="174"/>
     </row>
     <row r="18" spans="2:14" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="177" t="s">
+      <c r="B18" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="178"/>
-      <c r="D18" s="179"/>
-      <c r="E18" s="179"/>
-      <c r="F18" s="178" t="s">
+      <c r="C18" s="176"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="177"/>
+      <c r="F18" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="178"/>
-      <c r="H18" s="180"/>
-      <c r="I18" s="181"/>
-      <c r="J18" s="182" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="183"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="184" t="s">
-        <v>58</v>
-      </c>
-      <c r="N18" s="187" t="s">
+      <c r="G18" s="176"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="178" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="179"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="180" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="183" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="190" t="s">
+      <c r="B19" s="186" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="191"/>
-      <c r="D19" s="193" t="s">
+      <c r="C19" s="187"/>
+      <c r="D19" s="189" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="193"/>
-      <c r="F19" s="193"/>
-      <c r="G19" s="193"/>
-      <c r="H19" s="193"/>
-      <c r="I19" s="194"/>
-      <c r="J19" s="195" t="s">
+      <c r="E19" s="189"/>
+      <c r="F19" s="189"/>
+      <c r="G19" s="189"/>
+      <c r="H19" s="189"/>
+      <c r="I19" s="190"/>
+      <c r="J19" s="191" t="s">
         <v>39</v>
       </c>
-      <c r="K19" s="196"/>
-      <c r="L19" s="197"/>
-      <c r="M19" s="185"/>
-      <c r="N19" s="188"/>
+      <c r="K19" s="192"/>
+      <c r="L19" s="193"/>
+      <c r="M19" s="181"/>
+      <c r="N19" s="184"/>
     </row>
     <row r="20" spans="2:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="192"/>
-      <c r="C20" s="191"/>
+      <c r="B20" s="188"/>
+      <c r="C20" s="187"/>
       <c r="D20" s="33" t="s">
         <v>40</v>
       </c>
@@ -6189,7 +5657,7 @@
         <v>41</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20" s="33" t="s">
         <v>42</v>
@@ -6200,353 +5668,412 @@
       <c r="I20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="J20" s="195" t="s">
+      <c r="J20" s="191" t="s">
         <v>45</v>
       </c>
-      <c r="K20" s="196"/>
-      <c r="L20" s="197"/>
-      <c r="M20" s="186"/>
-      <c r="N20" s="189"/>
+      <c r="K20" s="192"/>
+      <c r="L20" s="193"/>
+      <c r="M20" s="182"/>
+      <c r="N20" s="185"/>
     </row>
     <row r="21" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="123">
-        <v>1</v>
-      </c>
-      <c r="C21" s="125"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="119"/>
-      <c r="N21" s="121"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="140"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="65"/>
     </row>
     <row r="22" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="131"/>
-      <c r="C22" s="132"/>
-      <c r="D22" s="132"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="120"/>
-      <c r="N22" s="122"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="69"/>
     </row>
     <row r="23" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="123">
-        <v>2</v>
-      </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="119"/>
-      <c r="N23" s="121"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="63"/>
+      <c r="K23" s="139"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="65"/>
     </row>
     <row r="24" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="131"/>
-      <c r="C24" s="132"/>
-      <c r="D24" s="132"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="117"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="120"/>
-      <c r="N24" s="122"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="69"/>
     </row>
     <row r="25" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="123">
-        <v>3</v>
-      </c>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="117"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="119"/>
-      <c r="N25" s="121"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="69"/>
     </row>
     <row r="26" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="131"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="120"/>
-      <c r="N26" s="122"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="69"/>
     </row>
     <row r="27" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="123">
-        <v>4</v>
-      </c>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="117"/>
-      <c r="L27" s="118"/>
-      <c r="M27" s="119"/>
-      <c r="N27" s="121"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="68"/>
+      <c r="N27" s="69"/>
     </row>
     <row r="28" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="131"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="134"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="117"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="120"/>
-      <c r="N28" s="122"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="69"/>
     </row>
     <row r="29" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="123">
-        <v>5</v>
-      </c>
-      <c r="C29" s="125"/>
-      <c r="D29" s="125"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="117"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="119"/>
-      <c r="N29" s="121"/>
-    </row>
-    <row r="30" spans="2:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="124"/>
-      <c r="C30" s="126"/>
-      <c r="D30" s="126"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="135"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="138"/>
-      <c r="M30" s="136"/>
-      <c r="N30" s="122"/>
-    </row>
-    <row r="31" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="B31" s="39"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-    </row>
-    <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="42"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-    </row>
-    <row r="33" spans="2:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="110" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="111"/>
-      <c r="D33" s="112" t="s">
+      <c r="B29" s="66"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="69"/>
+    </row>
+    <row r="30" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="57"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="65"/>
+    </row>
+    <row r="31" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="66"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="69"/>
+    </row>
+    <row r="32" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="57"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="65"/>
+    </row>
+    <row r="33" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="66"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="68"/>
+      <c r="N33" s="69"/>
+    </row>
+    <row r="34" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="57"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="65"/>
+    </row>
+    <row r="35" spans="2:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="70"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="141"/>
+      <c r="L35" s="142"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="78"/>
+    </row>
+    <row r="36" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="B36" s="35"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="24"/>
+    </row>
+    <row r="37" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="38"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+    </row>
+    <row r="38" spans="2:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="134" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="135"/>
+      <c r="D38" s="136" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="113"/>
-      <c r="F33" s="113"/>
-      <c r="G33" s="113"/>
-      <c r="H33" s="113"/>
-      <c r="I33" s="113"/>
-      <c r="J33" s="113"/>
-      <c r="K33" s="113"/>
-      <c r="L33" s="113"/>
-      <c r="M33" s="113"/>
-      <c r="N33" s="114"/>
-    </row>
-    <row r="34" spans="2:14" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="93"/>
-      <c r="D34" s="94" t="s">
+      <c r="E38" s="137"/>
+      <c r="F38" s="137"/>
+      <c r="G38" s="137"/>
+      <c r="H38" s="137"/>
+      <c r="I38" s="137"/>
+      <c r="J38" s="137"/>
+      <c r="K38" s="137"/>
+      <c r="L38" s="137"/>
+      <c r="M38" s="137"/>
+      <c r="N38" s="138"/>
+    </row>
+    <row r="39" spans="2:14" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="99" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" s="100"/>
+      <c r="D39" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="102"/>
+      <c r="F39" s="102"/>
+      <c r="G39" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="95"/>
-      <c r="F34" s="95"/>
-      <c r="G34" s="95" t="s">
+      <c r="H39" s="102"/>
+      <c r="I39" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="H34" s="95"/>
-      <c r="I34" s="95" t="s">
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="J34" s="95"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="95"/>
-      <c r="M34" s="96" t="s">
+      <c r="N39" s="104"/>
+    </row>
+    <row r="40" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="105"/>
+      <c r="C40" s="106"/>
+      <c r="D40" s="107"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="111"/>
+      <c r="I40" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="J40" s="113"/>
+      <c r="K40" s="113"/>
+      <c r="L40" s="113"/>
+      <c r="M40" s="114"/>
+      <c r="N40" s="115"/>
+    </row>
+    <row r="41" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="99" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="118"/>
+      <c r="D41" s="107"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="108"/>
+      <c r="G41" s="111"/>
+      <c r="H41" s="111"/>
+      <c r="I41" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="J41" s="113"/>
+      <c r="K41" s="113"/>
+      <c r="L41" s="113"/>
+      <c r="M41" s="114"/>
+      <c r="N41" s="115"/>
+    </row>
+    <row r="42" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="122"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="110"/>
+      <c r="G42" s="112"/>
+      <c r="H42" s="112"/>
+      <c r="I42" s="120"/>
+      <c r="J42" s="121"/>
+      <c r="K42" s="121"/>
+      <c r="L42" s="121"/>
+      <c r="M42" s="116"/>
+      <c r="N42" s="117"/>
+    </row>
+    <row r="43" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="N34" s="97"/>
-    </row>
-    <row r="35" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="98" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" s="99"/>
-      <c r="D35" s="100"/>
-      <c r="E35" s="101"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="J35" s="81"/>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
-      <c r="M35" s="106" t="s">
-        <v>95</v>
-      </c>
-      <c r="N35" s="107"/>
-    </row>
-    <row r="36" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="77" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="78"/>
-      <c r="D36" s="100"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="79" t="s">
-        <v>56</v>
-      </c>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="107"/>
-    </row>
-    <row r="37" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="84"/>
-      <c r="D37" s="102"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="105"/>
-      <c r="I37" s="80"/>
-      <c r="J37" s="82"/>
-      <c r="K37" s="82"/>
-      <c r="L37" s="82"/>
-      <c r="M37" s="108"/>
-      <c r="N37" s="109"/>
-    </row>
-    <row r="38" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="85" t="s">
+      <c r="C43" s="125"/>
+      <c r="D43" s="125"/>
+      <c r="E43" s="125"/>
+      <c r="F43" s="125"/>
+      <c r="G43" s="125"/>
+      <c r="H43" s="125"/>
+      <c r="I43" s="125"/>
+      <c r="J43" s="125"/>
+      <c r="K43" s="125"/>
+      <c r="L43" s="125"/>
+      <c r="M43" s="125"/>
+      <c r="N43" s="126"/>
+    </row>
+    <row r="44" spans="2:14" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="86"/>
-      <c r="D38" s="86"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="86"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="86"/>
-      <c r="M38" s="86"/>
-      <c r="N38" s="87"/>
-    </row>
-    <row r="39" spans="2:14" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="88" t="s">
+      <c r="C44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="96"/>
+      <c r="H44" s="96"/>
+      <c r="I44" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="89"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
-      <c r="M39" s="91"/>
-      <c r="N39" s="92"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B41" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
+      <c r="J44" s="97"/>
+      <c r="K44" s="97"/>
+      <c r="L44" s="97"/>
+      <c r="M44" s="97"/>
+      <c r="N44" s="98"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B46" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="72">
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="K9:N9"/>
@@ -6555,21 +6082,17 @@
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="K14:N14"/>
     <mergeCell ref="C13:N13"/>
-    <mergeCell ref="B16:N16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
     <mergeCell ref="M18:M20"/>
     <mergeCell ref="N18:N20"/>
     <mergeCell ref="B19:C20"/>
     <mergeCell ref="D19:I19"/>
     <mergeCell ref="J19:L19"/>
     <mergeCell ref="J20:L20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="B4:C4"/>
@@ -6591,81 +6114,40 @@
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:G8"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:N43"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="K8:N8"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
     <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="N21:N22"/>
     <mergeCell ref="K22:L22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="N23:N24"/>
     <mergeCell ref="K24:L24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:N33"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="M27:M28"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J36:L37"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:N38"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="B16:N16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="J44:N44"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="J39:N39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F37"/>
-    <mergeCell ref="G35:H37"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="M35:N37"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:F42"/>
+    <mergeCell ref="G40:H42"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="M40:N42"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:L42"/>
   </mergeCells>
-  <conditionalFormatting sqref="B35:C35">
+  <conditionalFormatting sqref="B40:C40">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Tiene menos de 6 meses desempeñando el puesto que es objeto de evaluación."</formula>
     </cfRule>
@@ -6673,26 +6155,18 @@
       <formula>"Tiene menos de 6 meses en la etapa de seguimiento, en el puesto evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D11 D18 L18 E21:E30 J21:J30 B35 B37">
+  <conditionalFormatting sqref="D11 D18 L18 B40 B42 J21:J35 E21:E35">
     <cfRule type="containsText" dxfId="1" priority="24" operator="containsText" text="[Seleccione]">
       <formula>NOT(ISERROR(SEARCH("[Seleccione]",B11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G31:G32">
+  <conditionalFormatting sqref="G36:G37">
     <cfRule type="containsText" dxfId="0" priority="23" operator="containsText" text="El peso total debe sumar 100%">
-      <formula>NOT(ISERROR(SEARCH("El peso total debe sumar 100%",G31)))</formula>
+      <formula>NOT(ISERROR(SEARCH("El peso total debe sumar 100%",G36)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37:C37">
-      <formula1>"[Seleccione],Sí,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35:C35">
-      <formula1>"[Seleccione], Tiene 6 meses o más desempeñando el puesto que es objeto de evaluación,Tiene menos de 6 meses desempeñando el puesto que es objeto de evaluación."</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B41" r:id="rId1" display="La versión descargable del formato se encuentra disponible en el Portafolio de la Gestión del Rendimiento."/>
+    <hyperlink ref="B46" r:id="rId1" display="La versión descargable del formato se encuentra disponible en el Portafolio de la Gestión del Rendimiento."/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="40" orientation="portrait" r:id="rId2"/>

--- a/src/assets/docs/modeloGDR.xlsx
+++ b/src/assets/docs/modeloGDR.xlsx
@@ -581,7 +581,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1547,17 +1547,127 @@
     <xf numFmtId="49" fontId="11" fillId="14" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1574,32 +1684,132 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1650,248 +1860,38 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2391,13 +2391,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>142876</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>79376</xdr:rowOff>
+      <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>168653</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>777876</xdr:rowOff>
+      <xdr:rowOff>740978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2412,7 +2412,7 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
@@ -2420,14 +2420,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect b="25952"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="142876" y="79376"/>
-          <a:ext cx="2327652" cy="857250"/>
+          <a:off x="142876" y="79375"/>
+          <a:ext cx="2385349" cy="814003"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2740,7 +2739,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:N46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="4.5546875" customWidth="1"/>
@@ -2758,7 +2757,7 @@
     <col min="15" max="26" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:14" ht="12" customHeight="1" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2773,26 +2772,26 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="2:14" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="82" t="s">
+    <row r="2" spans="2:14" ht="64.5" customHeight="1" thickBot="1">
+      <c r="B2" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="85" t="s">
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="86"/>
-    </row>
-    <row r="3" spans="2:14" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N2" s="118"/>
+    </row>
+    <row r="3" spans="2:14" ht="18.600000000000001" thickBot="1">
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2807,26 +2806,26 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="2:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="87" t="s">
+    <row r="4" spans="2:14" ht="39.75" customHeight="1" thickBot="1">
+      <c r="B4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="89" t="s">
+      <c r="C4" s="120"/>
+      <c r="D4" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="90"/>
-    </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="122"/>
+    </row>
+    <row r="5" spans="2:14" ht="15" thickBot="1">
       <c r="B5" s="5"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -2841,174 +2840,174 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="2:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="91" t="s">
+    <row r="6" spans="2:14" ht="21.6" thickBot="1">
+      <c r="B6" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="93"/>
-    </row>
-    <row r="7" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="94" t="s">
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="125"/>
+    </row>
+    <row r="7" spans="2:14" ht="15.6">
+      <c r="B7" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="94" t="s">
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="95"/>
-      <c r="J7" s="95"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="95"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="96"/>
-    </row>
-    <row r="8" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="99" t="s">
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="107"/>
+    </row>
+    <row r="8" spans="2:14" ht="29.25" customHeight="1">
+      <c r="B8" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="48" t="s">
+      <c r="C8" s="86"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="49"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="52"/>
-    </row>
-    <row r="9" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="99" t="s">
+      <c r="I8" s="81"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="84"/>
+    </row>
+    <row r="9" spans="2:14" ht="29.25" customHeight="1">
+      <c r="B9" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48" t="s">
+      <c r="C9" s="86"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="52"/>
-    </row>
-    <row r="10" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="97" t="s">
+      <c r="I9" s="81"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="84"/>
+    </row>
+    <row r="10" spans="2:14" ht="29.25" customHeight="1">
+      <c r="B10" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="98"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="97" t="s">
+      <c r="C10" s="109"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="52"/>
-    </row>
-    <row r="11" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="99" t="s">
+      <c r="I10" s="109"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="84"/>
+    </row>
+    <row r="11" spans="2:14" ht="29.25" customHeight="1">
+      <c r="B11" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="100"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="97" t="s">
+      <c r="C11" s="86"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="52"/>
-    </row>
-    <row r="12" spans="2:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="97" t="s">
+      <c r="I11" s="109"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="84"/>
+    </row>
+    <row r="12" spans="2:14" ht="49.5" customHeight="1">
+      <c r="B12" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="98"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="97" t="s">
+      <c r="C12" s="109"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="52"/>
-    </row>
-    <row r="13" spans="2:14" s="20" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="109"/>
+      <c r="J12" s="109"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="84"/>
+    </row>
+    <row r="13" spans="2:14" s="20" customFormat="1" ht="71.400000000000006" customHeight="1">
       <c r="B13" s="19"/>
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="152" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-    </row>
-    <row r="14" spans="2:14" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="53" t="s">
+      <c r="D13" s="152"/>
+      <c r="E13" s="152"/>
+      <c r="F13" s="152"/>
+      <c r="G13" s="152"/>
+      <c r="H13" s="152"/>
+      <c r="I13" s="152"/>
+      <c r="J13" s="152"/>
+      <c r="K13" s="152"/>
+      <c r="L13" s="152"/>
+      <c r="M13" s="152"/>
+      <c r="N13" s="152"/>
+    </row>
+    <row r="14" spans="2:14" ht="96" customHeight="1" thickBot="1">
+      <c r="B14" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="53" t="s">
+      <c r="C14" s="146"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="59"/>
-    </row>
-    <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I14" s="146"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="150"/>
+      <c r="M14" s="150"/>
+      <c r="N14" s="151"/>
+    </row>
+    <row r="15" spans="2:14" ht="15" thickBot="1">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -3023,93 +3022,93 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="2:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="116" t="s">
+    <row r="16" spans="2:14" ht="21.6" thickBot="1">
+      <c r="B16" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="118"/>
-    </row>
-    <row r="17" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="119" t="s">
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="96"/>
+    </row>
+    <row r="17" spans="2:14" ht="15.6">
+      <c r="B17" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="122" t="s">
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="K17" s="123"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="125" t="s">
+      <c r="K17" s="101"/>
+      <c r="L17" s="102"/>
+      <c r="M17" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="N17" s="126"/>
-    </row>
-    <row r="18" spans="2:14" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="75" t="s">
+      <c r="N17" s="104"/>
+    </row>
+    <row r="18" spans="2:14" ht="67.95" customHeight="1">
+      <c r="B18" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="76"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="76" t="s">
+      <c r="C18" s="141"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="76"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="80" t="s">
+      <c r="G18" s="141"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="K18" s="81"/>
+      <c r="K18" s="144"/>
       <c r="L18" s="22"/>
-      <c r="M18" s="61" t="s">
+      <c r="M18" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="64" t="s">
+      <c r="N18" s="129" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="67" t="s">
+    <row r="19" spans="2:14" ht="23.25" customHeight="1">
+      <c r="B19" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="70" t="s">
+      <c r="C19" s="133"/>
+      <c r="D19" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="72" t="s">
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="73"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="65"/>
-    </row>
-    <row r="20" spans="2:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="69"/>
-      <c r="C20" s="68"/>
+      <c r="K19" s="138"/>
+      <c r="L19" s="139"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="130"/>
+    </row>
+    <row r="20" spans="2:14" ht="31.95" customHeight="1">
+      <c r="B20" s="134"/>
+      <c r="C20" s="133"/>
       <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
@@ -3128,15 +3127,15 @@
       <c r="I20" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="72" t="s">
+      <c r="J20" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="K20" s="73"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="66"/>
-    </row>
-    <row r="21" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="138"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="131"/>
+    </row>
+    <row r="21" spans="2:14" ht="51" customHeight="1">
       <c r="B21" s="23"/>
       <c r="C21" s="24"/>
       <c r="D21" s="24"/>
@@ -3146,12 +3145,12 @@
       <c r="H21" s="27"/>
       <c r="I21" s="28"/>
       <c r="J21" s="29"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="103"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="46"/>
       <c r="M21" s="30"/>
       <c r="N21" s="31"/>
     </row>
-    <row r="22" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" ht="51" customHeight="1">
       <c r="B22" s="32"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -3161,12 +3160,12 @@
       <c r="H22" s="27"/>
       <c r="I22" s="28"/>
       <c r="J22" s="29"/>
-      <c r="K22" s="101"/>
-      <c r="L22" s="103"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="46"/>
       <c r="M22" s="34"/>
       <c r="N22" s="35"/>
     </row>
-    <row r="23" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" ht="51" customHeight="1">
       <c r="B23" s="23"/>
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
@@ -3176,12 +3175,12 @@
       <c r="H23" s="27"/>
       <c r="I23" s="28"/>
       <c r="J23" s="29"/>
-      <c r="K23" s="101"/>
-      <c r="L23" s="103"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="46"/>
       <c r="M23" s="30"/>
       <c r="N23" s="31"/>
     </row>
-    <row r="24" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" ht="51" customHeight="1">
       <c r="B24" s="32"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -3191,12 +3190,12 @@
       <c r="H24" s="27"/>
       <c r="I24" s="28"/>
       <c r="J24" s="29"/>
-      <c r="K24" s="101"/>
-      <c r="L24" s="103"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="46"/>
       <c r="M24" s="34"/>
       <c r="N24" s="35"/>
     </row>
-    <row r="25" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" ht="51" customHeight="1">
       <c r="B25" s="32"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -3206,12 +3205,12 @@
       <c r="H25" s="27"/>
       <c r="I25" s="28"/>
       <c r="J25" s="29"/>
-      <c r="K25" s="101"/>
-      <c r="L25" s="103"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="46"/>
       <c r="M25" s="34"/>
       <c r="N25" s="35"/>
     </row>
-    <row r="26" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" ht="51" customHeight="1">
       <c r="B26" s="32"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -3221,12 +3220,12 @@
       <c r="H26" s="27"/>
       <c r="I26" s="28"/>
       <c r="J26" s="29"/>
-      <c r="K26" s="101"/>
-      <c r="L26" s="103"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="46"/>
       <c r="M26" s="34"/>
       <c r="N26" s="35"/>
     </row>
-    <row r="27" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" ht="51" customHeight="1">
       <c r="B27" s="32"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -3236,12 +3235,12 @@
       <c r="H27" s="27"/>
       <c r="I27" s="28"/>
       <c r="J27" s="29"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="103"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="46"/>
       <c r="M27" s="34"/>
       <c r="N27" s="35"/>
     </row>
-    <row r="28" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" ht="51" customHeight="1">
       <c r="B28" s="32"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -3251,12 +3250,12 @@
       <c r="H28" s="27"/>
       <c r="I28" s="28"/>
       <c r="J28" s="29"/>
-      <c r="K28" s="101"/>
-      <c r="L28" s="103"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="46"/>
       <c r="M28" s="34"/>
       <c r="N28" s="35"/>
     </row>
-    <row r="29" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" ht="51" customHeight="1">
       <c r="B29" s="32"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -3266,12 +3265,12 @@
       <c r="H29" s="27"/>
       <c r="I29" s="28"/>
       <c r="J29" s="29"/>
-      <c r="K29" s="101"/>
-      <c r="L29" s="103"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="46"/>
       <c r="M29" s="34"/>
       <c r="N29" s="35"/>
     </row>
-    <row r="30" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" ht="51" customHeight="1">
       <c r="B30" s="23"/>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
@@ -3281,12 +3280,12 @@
       <c r="H30" s="27"/>
       <c r="I30" s="28"/>
       <c r="J30" s="29"/>
-      <c r="K30" s="101"/>
-      <c r="L30" s="103"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="46"/>
       <c r="M30" s="30"/>
       <c r="N30" s="31"/>
     </row>
-    <row r="31" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" ht="51" customHeight="1">
       <c r="B31" s="32"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -3296,12 +3295,12 @@
       <c r="H31" s="27"/>
       <c r="I31" s="28"/>
       <c r="J31" s="29"/>
-      <c r="K31" s="101"/>
-      <c r="L31" s="103"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="46"/>
       <c r="M31" s="34"/>
       <c r="N31" s="35"/>
     </row>
-    <row r="32" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" ht="51" customHeight="1">
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
@@ -3311,12 +3310,12 @@
       <c r="H32" s="27"/>
       <c r="I32" s="28"/>
       <c r="J32" s="29"/>
-      <c r="K32" s="101"/>
-      <c r="L32" s="103"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="46"/>
       <c r="M32" s="30"/>
       <c r="N32" s="31"/>
     </row>
-    <row r="33" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:14" ht="51" customHeight="1">
       <c r="B33" s="32"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -3326,12 +3325,12 @@
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
-      <c r="K33" s="101"/>
-      <c r="L33" s="103"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="46"/>
       <c r="M33" s="34"/>
       <c r="N33" s="35"/>
     </row>
-    <row r="34" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:14" ht="51" customHeight="1">
       <c r="B34" s="23"/>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
@@ -3341,12 +3340,12 @@
       <c r="H34" s="27"/>
       <c r="I34" s="28"/>
       <c r="J34" s="29"/>
-      <c r="K34" s="101"/>
-      <c r="L34" s="103"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="46"/>
       <c r="M34" s="30"/>
       <c r="N34" s="31"/>
     </row>
-    <row r="35" spans="2:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14" ht="51" customHeight="1" thickBot="1">
       <c r="B35" s="36"/>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -3356,12 +3355,12 @@
       <c r="H35" s="41"/>
       <c r="I35" s="42"/>
       <c r="J35" s="43"/>
-      <c r="K35" s="114"/>
-      <c r="L35" s="115"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="93"/>
       <c r="M35" s="38"/>
       <c r="N35" s="44"/>
     </row>
-    <row r="36" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:14" ht="23.4">
       <c r="B36" s="12"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -3376,7 +3375,7 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14" ht="15" thickBot="1">
       <c r="B37" s="15"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -3391,138 +3390,138 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="2:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="109" t="s">
+    <row r="38" spans="2:14" ht="75" customHeight="1">
+      <c r="B38" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="110"/>
-      <c r="D38" s="111" t="s">
+      <c r="C38" s="88"/>
+      <c r="D38" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="E38" s="112"/>
-      <c r="F38" s="112"/>
-      <c r="G38" s="112"/>
-      <c r="H38" s="112"/>
-      <c r="I38" s="112"/>
-      <c r="J38" s="112"/>
-      <c r="K38" s="112"/>
-      <c r="L38" s="112"/>
-      <c r="M38" s="112"/>
-      <c r="N38" s="113"/>
-    </row>
-    <row r="39" spans="2:14" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="132" t="s">
+      <c r="E38" s="90"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="90"/>
+      <c r="H38" s="90"/>
+      <c r="I38" s="90"/>
+      <c r="J38" s="90"/>
+      <c r="K38" s="90"/>
+      <c r="L38" s="90"/>
+      <c r="M38" s="90"/>
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" ht="58.95" customHeight="1">
+      <c r="B39" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="133"/>
-      <c r="D39" s="134" t="s">
+      <c r="C39" s="53"/>
+      <c r="D39" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="E39" s="135"/>
-      <c r="F39" s="135"/>
-      <c r="G39" s="135" t="s">
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="135"/>
-      <c r="I39" s="135" t="s">
+      <c r="H39" s="55"/>
+      <c r="I39" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="J39" s="135"/>
-      <c r="K39" s="135"/>
-      <c r="L39" s="135"/>
-      <c r="M39" s="136" t="s">
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="N39" s="137"/>
-    </row>
-    <row r="40" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="138"/>
-      <c r="C40" s="139"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="141"/>
-      <c r="G40" s="144"/>
-      <c r="H40" s="144"/>
+      <c r="N39" s="57"/>
+    </row>
+    <row r="40" spans="2:14" ht="48" customHeight="1">
+      <c r="B40" s="58"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
       <c r="I40" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="J40" s="146"/>
-      <c r="K40" s="146"/>
-      <c r="L40" s="146"/>
-      <c r="M40" s="78"/>
-      <c r="N40" s="79"/>
-    </row>
-    <row r="41" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="132" t="s">
+      <c r="J40" s="66"/>
+      <c r="K40" s="66"/>
+      <c r="L40" s="66"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="68"/>
+    </row>
+    <row r="41" spans="2:14" ht="48" customHeight="1">
+      <c r="B41" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="149"/>
-      <c r="D41" s="140"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="141"/>
-      <c r="G41" s="144"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="150" t="s">
+      <c r="C41" s="71"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
-      <c r="L41" s="146"/>
-      <c r="M41" s="78"/>
-      <c r="N41" s="79"/>
-    </row>
-    <row r="42" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="104"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="142"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="145"/>
-      <c r="H42" s="145"/>
-      <c r="I42" s="151"/>
-      <c r="J42" s="152"/>
-      <c r="K42" s="152"/>
-      <c r="L42" s="152"/>
-      <c r="M42" s="147"/>
-      <c r="N42" s="148"/>
-    </row>
-    <row r="43" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="106" t="s">
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="68"/>
+    </row>
+    <row r="42" spans="2:14" ht="48" customHeight="1" thickBot="1">
+      <c r="B42" s="75"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="74"/>
+      <c r="M42" s="69"/>
+      <c r="N42" s="70"/>
+    </row>
+    <row r="43" spans="2:14" ht="48" customHeight="1">
+      <c r="B43" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="107"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="107"/>
-      <c r="F43" s="107"/>
-      <c r="G43" s="107"/>
-      <c r="H43" s="107"/>
-      <c r="I43" s="107"/>
-      <c r="J43" s="107"/>
-      <c r="K43" s="107"/>
-      <c r="L43" s="107"/>
-      <c r="M43" s="107"/>
-      <c r="N43" s="108"/>
-    </row>
-    <row r="44" spans="2:14" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="127" t="s">
+      <c r="C43" s="78"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="79"/>
+    </row>
+    <row r="44" spans="2:14" ht="104.25" customHeight="1" thickBot="1">
+      <c r="B44" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="128"/>
-      <c r="D44" s="129"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="129"/>
-      <c r="G44" s="129"/>
-      <c r="H44" s="129"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
       <c r="I44" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J44" s="130"/>
-      <c r="K44" s="130"/>
-      <c r="L44" s="130"/>
-      <c r="M44" s="130"/>
-      <c r="N44" s="131"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="51"/>
+    </row>
+    <row r="46" spans="2:14">
       <c r="B46" s="21" t="s">
         <v>43</v>
       </c>
@@ -3533,18 +3532,64 @@
       <c r="G46" s="21"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ey8ZsNKWOqfFkRHoOXkEhXOis/k9o5m4/yvid215hrnuJUULq8SfaFAJAP0RQU9pf6voaxjhqQvCCZuVrBSA6w==" saltValue="PZ7nFJ3yRDx3NDfTJjA6cw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="x/6J+a6KNWyGCeyRKKn5FHJlrEY4NiA1OcA0xmMANbmYzYqFnapIYVF+nNvbD3yr5Y8LEVqf1hgPxEiAZXacig==" saltValue="jHtw/EV+dCMB27kTi1VNHg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="82">
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="C13:N13"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="B19:C20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:N43"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="B16:N16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="M17:N17"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="D44:H44"/>
     <mergeCell ref="J44:N44"/>
@@ -3561,62 +3606,16 @@
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="I41:I42"/>
     <mergeCell ref="J41:L42"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:N43"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="B16:N16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="B19:C20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="C13:N13"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K34:L34"/>
   </mergeCells>
   <conditionalFormatting sqref="B40:C40">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">

--- a/src/assets/docs/modeloGDR.xlsx
+++ b/src/assets/docs/modeloGDR.xlsx
@@ -581,7 +581,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="39">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -618,12 +618,6 @@
     <font>
       <b/>
       <sz val="25"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -840,7 +834,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -856,12 +850,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF012447"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF037341"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -932,7 +920,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1028,82 +1016,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1289,13 +1201,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -1305,59 +1217,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1372,30 +1232,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1410,488 +1246,595 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="21" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="14" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2053,8 +1996,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="77258" y="5349751"/>
-          <a:ext cx="530225" cy="488950"/>
+          <a:off x="77258" y="7290946"/>
+          <a:ext cx="543560" cy="488950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2739,7 +2682,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:N46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="4.5546875" customWidth="1"/>
@@ -2757,7 +2700,7 @@
     <col min="15" max="26" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="12" customHeight="1" thickBot="1">
+    <row r="1" spans="2:14" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2772,26 +2715,26 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="2:14" ht="64.5" customHeight="1" thickBot="1">
-      <c r="B2" s="114" t="s">
+    <row r="2" spans="2:14" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="117" t="s">
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="134"/>
+      <c r="M2" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="118"/>
-    </row>
-    <row r="3" spans="2:14" ht="18.600000000000001" thickBot="1">
+      <c r="N2" s="132"/>
+    </row>
+    <row r="3" spans="2:14" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2806,26 +2749,26 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="2:14" ht="39.75" customHeight="1" thickBot="1">
-      <c r="B4" s="119" t="s">
+    <row r="4" spans="2:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121" t="s">
+      <c r="C4" s="131"/>
+      <c r="D4" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="122"/>
-    </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1">
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="129"/>
+    </row>
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -2840,174 +2783,174 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="2:14" ht="21.6" thickBot="1">
-      <c r="B6" s="123" t="s">
+    <row r="6" spans="2:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
-      <c r="L6" s="124"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="125"/>
-    </row>
-    <row r="7" spans="2:14" ht="15.6">
-      <c r="B7" s="105" t="s">
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="112"/>
+    </row>
+    <row r="7" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="105" t="s">
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="107"/>
-    </row>
-    <row r="8" spans="2:14" ht="29.25" customHeight="1">
-      <c r="B8" s="85" t="s">
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="126"/>
+    </row>
+    <row r="8" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="86"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="80" t="s">
+      <c r="C8" s="123"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="81"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="84"/>
-    </row>
-    <row r="9" spans="2:14" ht="29.25" customHeight="1">
-      <c r="B9" s="85" t="s">
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="120"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="121"/>
+    </row>
+    <row r="9" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="111"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="80" t="s">
+      <c r="C9" s="123"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="81"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="84"/>
-    </row>
-    <row r="10" spans="2:14" ht="29.25" customHeight="1">
-      <c r="B10" s="108" t="s">
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="121"/>
+    </row>
+    <row r="10" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="109"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="108" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="109"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="84"/>
-    </row>
-    <row r="11" spans="2:14" ht="29.25" customHeight="1">
-      <c r="B11" s="85" t="s">
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="121"/>
+    </row>
+    <row r="11" spans="2:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="86"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="108" t="s">
+      <c r="C11" s="123"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="109"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="84"/>
-    </row>
-    <row r="12" spans="2:14" ht="49.5" customHeight="1">
-      <c r="B12" s="108" t="s">
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="121"/>
+    </row>
+    <row r="12" spans="2:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="109"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="108" t="s">
+      <c r="C12" s="28"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="109"/>
-      <c r="J12" s="109"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="84"/>
-    </row>
-    <row r="13" spans="2:14" s="20" customFormat="1" ht="71.400000000000006" customHeight="1">
-      <c r="B13" s="19"/>
-      <c r="C13" s="152" t="s">
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="121"/>
+    </row>
+    <row r="13" spans="2:14" s="18" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="17"/>
+      <c r="C13" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="152"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="152"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="152"/>
-      <c r="I13" s="152"/>
-      <c r="J13" s="152"/>
-      <c r="K13" s="152"/>
-      <c r="L13" s="152"/>
-      <c r="M13" s="152"/>
-      <c r="N13" s="152"/>
-    </row>
-    <row r="14" spans="2:14" ht="96" customHeight="1" thickBot="1">
-      <c r="B14" s="145" t="s">
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="2:14" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="146"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="145" t="s">
+      <c r="C14" s="118"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="146"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="150"/>
-      <c r="N14" s="151"/>
-    </row>
-    <row r="15" spans="2:14" ht="15" thickBot="1">
+      <c r="I14" s="117"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="115"/>
+    </row>
+    <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -3022,351 +2965,351 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="2:14" ht="21.6" thickBot="1">
-      <c r="B16" s="94" t="s">
+    <row r="16" spans="2:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="96"/>
-    </row>
-    <row r="17" spans="2:14" ht="15.6">
-      <c r="B17" s="97" t="s">
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="112"/>
+    </row>
+    <row r="17" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="K17" s="101"/>
-      <c r="L17" s="102"/>
-      <c r="M17" s="103" t="s">
+      <c r="K17" s="105"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="N17" s="104"/>
-    </row>
-    <row r="18" spans="2:14" ht="67.95" customHeight="1">
-      <c r="B18" s="140" t="s">
+      <c r="N17" s="103"/>
+    </row>
+    <row r="18" spans="2:14" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="141"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="141" t="s">
+      <c r="C18" s="98"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="141"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="143" t="s">
+      <c r="G18" s="98"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="K18" s="144"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="126" t="s">
+      <c r="K18" s="95"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="129" t="s">
+      <c r="N18" s="33" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="23.25" customHeight="1">
-      <c r="B19" s="132" t="s">
+    <row r="19" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="133"/>
-      <c r="D19" s="135" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="135"/>
-      <c r="F19" s="135"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="137" t="s">
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="138"/>
-      <c r="L19" s="139"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="130"/>
-    </row>
-    <row r="20" spans="2:14" ht="31.95" customHeight="1">
-      <c r="B20" s="134"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="10" t="s">
+      <c r="K19" s="87"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="93"/>
+      <c r="N19" s="34"/>
+    </row>
+    <row r="20" spans="2:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="137" t="s">
+      <c r="J20" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="K20" s="138"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="128"/>
-      <c r="N20" s="131"/>
-    </row>
-    <row r="21" spans="2:14" ht="51" customHeight="1">
-      <c r="B21" s="23"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="31"/>
-    </row>
-    <row r="22" spans="2:14" ht="51" customHeight="1">
-      <c r="B22" s="32"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="35"/>
-    </row>
-    <row r="23" spans="2:14" ht="51" customHeight="1">
-      <c r="B23" s="23"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="31"/>
-    </row>
-    <row r="24" spans="2:14" ht="51" customHeight="1">
-      <c r="B24" s="32"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="35"/>
-    </row>
-    <row r="25" spans="2:14" ht="51" customHeight="1">
-      <c r="B25" s="32"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="35"/>
-    </row>
-    <row r="26" spans="2:14" ht="51" customHeight="1">
-      <c r="B26" s="32"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="35"/>
-    </row>
-    <row r="27" spans="2:14" ht="51" customHeight="1">
-      <c r="B27" s="32"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="35"/>
-    </row>
-    <row r="28" spans="2:14" ht="51" customHeight="1">
-      <c r="B28" s="32"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="35"/>
-    </row>
-    <row r="29" spans="2:14" ht="51" customHeight="1">
-      <c r="B29" s="32"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="35"/>
-    </row>
-    <row r="30" spans="2:14" ht="51" customHeight="1">
-      <c r="B30" s="23"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="31"/>
-    </row>
-    <row r="31" spans="2:14" ht="51" customHeight="1">
-      <c r="B31" s="32"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="35"/>
-    </row>
-    <row r="32" spans="2:14" ht="51" customHeight="1">
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="31"/>
-    </row>
-    <row r="33" spans="2:14" ht="51" customHeight="1">
-      <c r="B33" s="32"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="35"/>
-    </row>
-    <row r="34" spans="2:14" ht="51" customHeight="1">
-      <c r="B34" s="23"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="31"/>
-    </row>
-    <row r="35" spans="2:14" ht="51" customHeight="1" thickBot="1">
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="38"/>
-      <c r="N35" s="44"/>
-    </row>
-    <row r="36" spans="2:14" ht="23.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="14"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="35"/>
+    </row>
+    <row r="21" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="135"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="138"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="140"/>
+      <c r="L21" s="140"/>
+      <c r="M21" s="141"/>
+      <c r="N21" s="142"/>
+    </row>
+    <row r="22" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="144"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="145"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="139"/>
+      <c r="J22" s="139"/>
+      <c r="K22" s="140"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="147"/>
+    </row>
+    <row r="23" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="135"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="136"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="139"/>
+      <c r="J23" s="139"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="141"/>
+      <c r="N23" s="142"/>
+    </row>
+    <row r="24" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="144"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="145"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="139"/>
+      <c r="K24" s="140"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="146"/>
+      <c r="N24" s="147"/>
+    </row>
+    <row r="25" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="144"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="145"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="140"/>
+      <c r="L25" s="140"/>
+      <c r="M25" s="146"/>
+      <c r="N25" s="147"/>
+    </row>
+    <row r="26" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="144"/>
+      <c r="C26" s="137"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="145"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="146"/>
+      <c r="N26" s="147"/>
+    </row>
+    <row r="27" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="144"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="139"/>
+      <c r="K27" s="140"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="146"/>
+      <c r="N27" s="147"/>
+    </row>
+    <row r="28" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="144"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="145"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="146"/>
+      <c r="N28" s="147"/>
+    </row>
+    <row r="29" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="144"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="139"/>
+      <c r="K29" s="140"/>
+      <c r="L29" s="140"/>
+      <c r="M29" s="146"/>
+      <c r="N29" s="147"/>
+    </row>
+    <row r="30" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="135"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="136"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="139"/>
+      <c r="K30" s="140"/>
+      <c r="L30" s="140"/>
+      <c r="M30" s="141"/>
+      <c r="N30" s="142"/>
+    </row>
+    <row r="31" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="144"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="139"/>
+      <c r="K31" s="140"/>
+      <c r="L31" s="140"/>
+      <c r="M31" s="146"/>
+      <c r="N31" s="147"/>
+    </row>
+    <row r="32" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="135"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="136"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="139"/>
+      <c r="J32" s="139"/>
+      <c r="K32" s="140"/>
+      <c r="L32" s="140"/>
+      <c r="M32" s="141"/>
+      <c r="N32" s="142"/>
+    </row>
+    <row r="33" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="144"/>
+      <c r="C33" s="137"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="139"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="140"/>
+      <c r="L33" s="140"/>
+      <c r="M33" s="146"/>
+      <c r="N33" s="147"/>
+    </row>
+    <row r="34" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="135"/>
+      <c r="C34" s="136"/>
+      <c r="D34" s="136"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="136"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="139"/>
+      <c r="J34" s="139"/>
+      <c r="K34" s="140"/>
+      <c r="L34" s="140"/>
+      <c r="M34" s="141"/>
+      <c r="N34" s="142"/>
+    </row>
+    <row r="35" spans="2:14" s="143" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="144"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="145"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="139"/>
+      <c r="J35" s="139"/>
+      <c r="K35" s="140"/>
+      <c r="L35" s="140"/>
+      <c r="M35" s="146"/>
+      <c r="N35" s="147"/>
+    </row>
+    <row r="36" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="12"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="7"/>
@@ -3375,13 +3318,13 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="2:14" ht="15" thickBot="1">
-      <c r="B37" s="15"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+    <row r="37" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="13"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="16"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="7"/>
@@ -3390,174 +3333,192 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="2:14" ht="75" customHeight="1">
-      <c r="B38" s="87" t="s">
+    <row r="38" spans="2:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="89" t="s">
+      <c r="C38" s="52"/>
+      <c r="D38" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E38" s="90"/>
-      <c r="F38" s="90"/>
-      <c r="G38" s="90"/>
-      <c r="H38" s="90"/>
-      <c r="I38" s="90"/>
-      <c r="J38" s="90"/>
-      <c r="K38" s="90"/>
-      <c r="L38" s="90"/>
-      <c r="M38" s="90"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" ht="58.95" customHeight="1">
-      <c r="B39" s="52" t="s">
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="55"/>
+    </row>
+    <row r="39" spans="2:14" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="53"/>
-      <c r="D39" s="54" t="s">
+      <c r="C39" s="62"/>
+      <c r="D39" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55" t="s">
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55" t="s">
+      <c r="H39" s="64"/>
+      <c r="I39" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="56" t="s">
+      <c r="J39" s="64"/>
+      <c r="K39" s="64"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="N39" s="57"/>
-    </row>
-    <row r="40" spans="2:14" ht="48" customHeight="1">
-      <c r="B40" s="58"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="18" t="s">
+      <c r="N39" s="66"/>
+    </row>
+    <row r="40" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="67"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="68"/>
-    </row>
-    <row r="41" spans="2:14" ht="48" customHeight="1">
-      <c r="B41" s="52" t="s">
+      <c r="J40" s="75"/>
+      <c r="K40" s="75"/>
+      <c r="L40" s="75"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="40"/>
+    </row>
+    <row r="41" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="71"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="72" t="s">
+      <c r="C41" s="78"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="68"/>
-    </row>
-    <row r="42" spans="2:14" ht="48" customHeight="1" thickBot="1">
-      <c r="B42" s="75"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="63"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="74"/>
-      <c r="L42" s="74"/>
-      <c r="M42" s="69"/>
-      <c r="N42" s="70"/>
-    </row>
-    <row r="43" spans="2:14" ht="48" customHeight="1">
-      <c r="B43" s="77" t="s">
+      <c r="J41" s="75"/>
+      <c r="K41" s="75"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="40"/>
+    </row>
+    <row r="42" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="46"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
+      <c r="M42" s="76"/>
+      <c r="N42" s="77"/>
+    </row>
+    <row r="43" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="79"/>
-    </row>
-    <row r="44" spans="2:14" ht="104.25" customHeight="1" thickBot="1">
-      <c r="B44" s="47" t="s">
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="50"/>
+    </row>
+    <row r="44" spans="2:14" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="48"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="17" t="s">
+      <c r="C44" s="57"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="51"/>
-    </row>
-    <row r="46" spans="2:14">
-      <c r="B46" s="21" t="s">
+      <c r="J44" s="59"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="59"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="60"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B46" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="x/6J+a6KNWyGCeyRKKn5FHJlrEY4NiA1OcA0xmMANbmYzYqFnapIYVF+nNvbD3yr5Y8LEVqf1hgPxEiAZXacig==" saltValue="jHtw/EV+dCMB27kTi1VNHg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="82">
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="C13:N13"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="B19:C20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B16:N16"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="J44:N44"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:F42"/>
+    <mergeCell ref="G40:H42"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="M40:N42"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:L42"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:N43"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="H7:N7"/>
     <mergeCell ref="B12:C12"/>
@@ -3574,48 +3535,30 @@
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:G8"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:N43"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="B16:N16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="J44:N44"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:F42"/>
-    <mergeCell ref="G40:H42"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="M40:N42"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:L42"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="B19:C20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="C13:N13"/>
   </mergeCells>
   <conditionalFormatting sqref="B40:C40">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -3639,7 +3582,7 @@
     <hyperlink ref="B46" r:id="rId1" display="La versión descargable del formato se encuentra disponible en el Portafolio de la Gestión del Rendimiento."/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="40" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="37" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
   <legacyDrawing r:id="rId4"/>
 </worksheet>
